--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -547,7 +547,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>17882.9</v>
+        <v>17879.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>35.17</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>508.4702871765709</v>
+        <v>508.5224687144483</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1427601793570292</v>
+        <v>0.1430665752008382</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02843332385555871</v>
+        <v>0.02844141069397042</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>77.10407174281168</v>
+        <v>77.22663008033528</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>44.87364576526774</v>
+        <v>44.91041326652483</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>24.15932768179862</v>
+        <v>24.16854581961379</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12284.30028435702</v>
+        <v>12290.24858542826</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.3130700118908553</v>
+        <v>-0.3126124624683222</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>37.51857130442404</v>
+        <v>37.54178735521779</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19077.07872561514</v>
+        <v>19090.84238582821</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.06677768849656029</v>
+        <v>0.06774139235545484</v>
       </c>
     </row>
     <row r="15"/>
@@ -4925,7 +4925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5016,6 +5016,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>17879.65</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.689393939394</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.143066575201</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>17879.65</v>
+        <v>17878.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>508.5224687144483</v>
+        <v>508.4926052332196</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1430665752008382</v>
+        <v>0.1428530250344324</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>77.22663008033528</v>
+        <v>77.14121001377296</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>44.91041326652483</v>
+        <v>44.88478724655613</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>24.16854581961379</v>
+        <v>24.16212101032164</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12290.24858542826</v>
+        <v>12286.25986049876</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>-0.3126124624683222</v>
+        <v>-0.3127951931080307</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>37.54178735521779</v>
+        <v>37.52560635403756</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19090.84238582821</v>
+        <v>19081.49333792082</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.06774139235545484</v>
+        <v>0.0672811818554484</v>
       </c>
     </row>
     <row r="15"/>
@@ -4925,7 +4925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5049,6 +5049,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>17878.6</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>35.16</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.689393939394</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.142853025034</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>17878.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>35.16</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.6893939393939394</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>508.4926052332196</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.1428530250344324</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>31.06060606060606</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>77.14121001377296</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>44.88478724655613</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>24.16212101032164</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>12286.25986049876</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>-0.3127951931080307</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>37.52560635403756</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>19081.49333792082</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.0672811818554484</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,19 +811,19 @@
       <c r="B18" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.3905951766518958</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.2115207044287035</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.1805472301841492</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="30" t="n">
         <v>0.184129263461102</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -821,19 +836,19 @@
       <c r="B19" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.03458683366427362</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1641163300520954</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.07036659518783939</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.1630328647790763</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -846,19 +861,19 @@
       <c r="B20" t="n">
         <v>12</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.05128555869590079</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1982429041594077</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1496483806058929</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.1669110499029909</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -871,19 +886,19 @@
       <c r="B21" t="n">
         <v>11</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.07652386056999227</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1173100602015256</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1643476874521761</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="30" t="n">
         <v>0.1754930481859425</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="30" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -896,21 +911,20 @@
       <c r="B22" t="n">
         <v>12</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.03252753981787726</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1515295920381106</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1470358414538852</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1046,16 +1060,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>6725.2</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>47.88</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1065,16 +1079,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>7205.85</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>38.01</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1084,16 +1098,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>7474.8</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>32.39</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1103,16 +1117,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>7658.4</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>31.98</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1122,16 +1136,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>7502.95</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>21.79</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1141,16 +1155,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>8278.549999999999</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>32.88</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1160,16 +1174,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>8513.5</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>30.73</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1179,16 +1193,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>8186.3</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>27.68</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1198,16 +1212,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>8410.75</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>28.51</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1217,16 +1231,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>8395.4</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>28.52</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1236,16 +1250,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>7810.45</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>25.05</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1255,16 +1269,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>8183.75</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>22.24</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1274,16 +1288,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>8168.85</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>22.1</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1293,16 +1307,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>7783.4</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>19.46</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1312,16 +1326,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>7297.65</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>18.44</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1331,16 +1345,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>8170.8</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>20.1</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1350,16 +1364,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>8556</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>21.88</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1369,16 +1383,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>8332.700000000001</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>21.71</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1388,16 +1402,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>8690.35</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>21.75</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1407,16 +1421,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>8855.6</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>24.65</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1426,16 +1440,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>8751.75</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>24.3</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1445,16 +1459,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>8638</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>23.22</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1464,16 +1478,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>8456.700000000001</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>22.03</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1483,16 +1497,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>8466.799999999999</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>21.63</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1502,16 +1516,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>8962.85</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>22.89</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1521,16 +1535,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>9539.9</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>22.71</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1540,16 +1554,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>10126.85</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>24.03</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1559,16 +1573,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>10822.5</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>24.49</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1578,16 +1592,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>11182.65</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>20.76</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1597,16 +1611,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>11611.65</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>21.99</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1616,16 +1630,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>11068.85</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>20.64</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1635,16 +1649,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>12200.6</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>19.73</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1654,16 +1668,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>13144.95</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>21.41</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1673,16 +1687,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>13620.6</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>21.56</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1692,16 +1706,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>13745.85</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>21.03</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1711,16 +1725,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>13526.5</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>33.17</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1730,16 +1744,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>14161.9</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>34.31</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1749,16 +1763,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>14443.45</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>41.41</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1768,16 +1782,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>15711.15</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>44.27</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1787,16 +1801,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>16661.65</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>49.81</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1806,16 +1820,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>16618.8</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>47.82</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1825,16 +1839,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>16883.35</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>50.95</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1844,16 +1858,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>15539.6</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>48.4</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1863,16 +1877,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>15697.75</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>47.49</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1882,16 +1896,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>15974.1</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1901,16 +1915,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>14948.1</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>42.94</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1920,16 +1934,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>13540.15</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>37.29</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1939,16 +1953,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>14561.6</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>39.22</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1958,16 +1972,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>15314.1</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>38.62</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1977,16 +1991,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>15998.9</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>38.96</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1996,16 +2010,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>16846.2</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>40.48</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2015,16 +2029,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>16212.45</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>37.97</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2034,16 +2048,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>15714.75</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>35.32</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2053,16 +2067,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>15945.4</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>32.97</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2072,16 +2086,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>17006.3</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>34.48</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2091,16 +2105,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>17423.05</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>33.92</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2110,16 +2124,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>17254.05</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>33.72</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2129,16 +2143,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>16693.25</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>32.32</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2148,16 +2162,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>16765.6</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>32.33</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2167,16 +2181,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>14983.35</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>32.13</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2186,16 +2200,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>16882.5</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>34.17</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2205,16 +2219,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>17490.55</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>32.84</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2224,16 +2238,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>17594.9</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>32.87</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2243,16 +2257,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>18105.85</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>36.6</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2262,16 +2276,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>18491.45</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>36.37</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2373,13 +2387,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>40999</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>2301</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>18.3</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2387,12 +2401,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$59,D2,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$59,D2,$C$2:$C$59,C2)+1)/2)/COUNTIFS($D$2:$D$59,D2,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2400,31 +2414,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>41090</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>2137</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>13.17</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2432,12 +2446,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$59,D3,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$59,D3,$C$2:$C$59,C3)+1)/2)/COUNTIFS($D$2:$D$59,D3,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2445,31 +2459,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>41182</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>2252.45</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>14.59</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2477,12 +2491,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$59,D4,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$59,D4,$C$2:$C$59,C4)+1)/2)/COUNTIFS($D$2:$D$59,D4,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2490,31 +2504,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>41274</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>2369.5</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>15.11</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2522,12 +2536,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$59,D5,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$59,D5,$C$2:$C$59,C5)+1)/2)/COUNTIFS($D$2:$D$59,D5,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2535,31 +2549,31 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="30">
         <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>41364</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>1933</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>11.72</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2567,15 +2581,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$59,D6,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$59,D6,$C$2:$C$59,C6)+1)/2)/COUNTIFS($D$2:$D$59,D6,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2583,31 +2597,31 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="30">
         <f>IFERROR((B46/B6)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>41455</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>1891.65</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>12.38</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2615,15 +2629,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$59,D7,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$59,D7,$C$2:$C$59,C7)+1)/2)/COUNTIFS($D$2:$D$59,D7,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2631,31 +2645,31 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="30">
         <f>IFERROR((B47/B7)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>41547</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>1884.35</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>9.449999999999999</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2663,15 +2677,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$59,D8,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$59,D8,$C$2:$C$59,C8)+1)/2)/COUNTIFS($D$2:$D$59,D8,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2679,31 +2693,31 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="30">
         <f>IFERROR((B48/B8)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>41639</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>2302.75</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>12.86</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2711,15 +2725,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$59,D9,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$59,D9,$C$2:$C$59,C9)+1)/2)/COUNTIFS($D$2:$D$59,D9,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2727,31 +2741,31 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="30">
         <f>IFERROR((B49/B9)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>41729</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>2465.15</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>12.89</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2759,15 +2773,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$59,D10,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$59,D10,$C$2:$C$59,C10)+1)/2)/COUNTIFS($D$2:$D$59,D10,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2775,31 +2789,31 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="30">
         <f>IFERROR((B50/B10)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>41820</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>3380.25</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>18.82</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2807,15 +2821,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$59,D11,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$59,D11,$C$2:$C$59,C11)+1)/2)/COUNTIFS($D$2:$D$59,D11,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2823,31 +2837,31 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="30">
         <f>IFERROR((B51/B11)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>41912</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>3127.5</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>16.11</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2855,15 +2869,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$59,D12,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$59,D12,$C$2:$C$59,C12)+1)/2)/COUNTIFS($D$2:$D$59,D12,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2871,31 +2885,31 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="30">
         <f>IFERROR((B52/B12)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>42004</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>3363.45</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>16.34</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2903,15 +2917,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$59,D13,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$59,D13,$C$2:$C$59,C13)+1)/2)/COUNTIFS($D$2:$D$59,D13,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2919,31 +2933,31 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="30">
         <f>IFERROR((B53/B13)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>42094</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>3373.65</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>14.42</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2951,15 +2965,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$59,D14,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$59,D14,$C$2:$C$59,C14)+1)/2)/COUNTIFS($D$2:$D$59,D14,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -2967,31 +2981,31 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="30">
         <f>IFERROR((B54/B14)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>42185</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>3212.45</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>15.53</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2999,15 +3013,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$59,D15,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$59,D15,$C$2:$C$59,C15)+1)/2)/COUNTIFS($D$2:$D$59,D15,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3015,31 +3029,31 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="30">
         <f>IFERROR((B55/B15)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>42277</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>3201.35</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>18.4</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3047,15 +3061,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$59,D16,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$59,D16,$C$2:$C$59,C16)+1)/2)/COUNTIFS($D$2:$D$59,D16,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3063,31 +3077,31 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="30">
         <f>IFERROR((B56/B16)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>3415.2</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>21.84</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3095,15 +3109,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$59,D17,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$59,D17,$C$2:$C$59,C17)+1)/2)/COUNTIFS($D$2:$D$59,D17,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3111,31 +3125,31 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="30">
         <f>IFERROR((B57/B17)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>3200.6</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>26.86</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3143,15 +3157,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$59,D18,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$59,D18,$C$2:$C$59,C18)+1)/2)/COUNTIFS($D$2:$D$59,D18,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3159,31 +3173,31 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="30">
         <f>IFERROR((B58/B18)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>3492.9</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>49.2</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3191,15 +3205,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$59,D19,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$59,D19,$C$2:$C$59,C19)+1)/2)/COUNTIFS($D$2:$D$59,D19,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3207,31 +3221,31 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="30">
         <f>IFERROR((B59/B19)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>3959.65</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>41.99</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3239,15 +3253,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$59,D20,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$59,D20,$C$2:$C$59,C20)+1)/2)/COUNTIFS($D$2:$D$59,D20,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3255,28 +3269,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>3662.3</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>32.65</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3284,15 +3298,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$59,D21,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$59,D21,$C$2:$C$59,C21)+1)/2)/COUNTIFS($D$2:$D$59,D21,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3300,28 +3314,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>4383.65</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>49.78</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3329,15 +3343,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$59,D22,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$59,D22,$C$2:$C$59,C22)+1)/2)/COUNTIFS($D$2:$D$59,D22,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3345,28 +3359,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>4519.75</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>62.93</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3374,15 +3388,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$59,D23,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$59,D23,$C$2:$C$59,C23)+1)/2)/COUNTIFS($D$2:$D$59,D23,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3390,28 +3404,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>4687.5</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>83.47</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3419,15 +3433,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$59,D24,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$59,D24,$C$2:$C$59,C24)+1)/2)/COUNTIFS($D$2:$D$59,D24,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3435,28 +3449,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>5540.15</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>97.06</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3464,15 +3478,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$59,D25,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$59,D25,$C$2:$C$59,C25)+1)/2)/COUNTIFS($D$2:$D$59,D25,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3480,28 +3494,28 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="30">
         <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L25" s="16" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>4975.3</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>91.53</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3509,15 +3523,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$59,D26,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$59,D26,$C$2:$C$59,C26)+1)/2)/COUNTIFS($D$2:$D$59,D26,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3525,28 +3539,28 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="30">
         <f>IFERROR((B46/B26)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L26" s="16" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>4850.7</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>50.03</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3554,15 +3568,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$59,D27,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$59,D27,$C$2:$C$59,C27)+1)/2)/COUNTIFS($D$2:$D$59,D27,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3570,28 +3584,28 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="30">
         <f>IFERROR((B47/B27)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L27" s="16" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>4622.85</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>70.43000000000001</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3599,15 +3613,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$59,D28,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$59,D28,$C$2:$C$59,C28)+1)/2)/COUNTIFS($D$2:$D$59,D28,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3615,28 +3629,28 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="30">
         <f>IFERROR((B48/B28)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L28" s="16" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>4930.95</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>51.05</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3644,15 +3658,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$59,D29,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$59,D29,$C$2:$C$59,C29)+1)/2)/COUNTIFS($D$2:$D$59,D29,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3660,28 +3674,28 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="30">
         <f>IFERROR((B49/B29)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L29" s="16" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>5077.85</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>35.15</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3689,15 +3703,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$59,D30,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$59,D30,$C$2:$C$59,C30)+1)/2)/COUNTIFS($D$2:$D$59,D30,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3705,28 +3719,28 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="30">
         <f>IFERROR((B50/B30)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L30" s="16" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>4872</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>30.46</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3734,15 +3748,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$59,D31,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$59,D31,$C$2:$C$59,C31)+1)/2)/COUNTIFS($D$2:$D$59,D31,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3750,28 +3764,28 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="30">
         <f>IFERROR((B51/B31)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L31" s="16" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>4394</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>20.98</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3779,15 +3793,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$59,D32,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$59,D32,$C$2:$C$59,C32)+1)/2)/COUNTIFS($D$2:$D$59,D32,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3795,28 +3809,28 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="30">
         <f>IFERROR((B52/B32)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L32" s="16" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>4701.1</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>23.44</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3824,15 +3838,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$59,D33,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$59,D33,$C$2:$C$59,C33)+1)/2)/COUNTIFS($D$2:$D$59,D33,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3840,28 +3854,28 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="30">
         <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="30">
         <f>IFERROR((B53/B33)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L33" s="16" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>3180.6</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>16.1</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3869,15 +3883,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$59,D34,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$59,D34,$C$2:$C$59,C34)+1)/2)/COUNTIFS($D$2:$D$59,D34,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3885,42 +3899,42 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="30">
         <f>IFERROR((B46/B34)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="30">
         <f>IFERROR((B54/B34)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L34" s="16" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>4094.25</v>
       </c>
-      <c r="C35" s="7" t="n"/>
+      <c r="C35" s="25" t="n"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$59,D35,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$59,D35,$C$2:$C$59,C35)+1)/2)/COUNTIFS($D$2:$D$59,D35,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3928,42 +3942,42 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="30">
         <f>IFERROR((B47/B35)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="30">
         <f>IFERROR((B55/B35)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L35" s="16" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>4666.55</v>
       </c>
-      <c r="C36" s="7" t="n"/>
+      <c r="C36" s="25" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$59,D36,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$59,D36,$C$2:$C$59,C36)+1)/2)/COUNTIFS($D$2:$D$59,D36,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -3971,28 +3985,28 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16">
+      <c r="J36" s="30">
         <f>IFERROR((B48/B36)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="30">
         <f>IFERROR((B56/B36)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L36" s="16" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>5872.6</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>186.09</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4000,15 +4014,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$59,D37,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$59,D37,$C$2:$C$59,C37)+1)/2)/COUNTIFS($D$2:$D$59,D37,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4016,28 +4030,28 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="30">
         <f>IFERROR((B49/B37)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="30">
         <f>IFERROR((B57/B37)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L37" s="16" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>6772.1</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>48.42</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4045,15 +4059,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$59,D38,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$59,D38,$C$2:$C$59,C38)+1)/2)/COUNTIFS($D$2:$D$59,D38,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4061,28 +4075,28 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="30">
         <f>IFERROR((B50/B38)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="30">
         <f>IFERROR((B58/B38)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L38" s="16" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>7474.8</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>32.39</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4090,15 +4104,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$59,D39,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$59,D39,$C$2:$C$59,C39)+1)/2)/COUNTIFS($D$2:$D$59,D39,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4106,28 +4120,28 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="30">
         <f>IFERROR((B51/B39)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="30">
         <f>IFERROR((B59/B39)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L39" s="16" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>8278.549999999999</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>32.88</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4135,15 +4149,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$59,D40,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$59,D40,$C$2:$C$59,C40)+1)/2)/COUNTIFS($D$2:$D$59,D40,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4151,25 +4165,25 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="30">
         <f>IFERROR((B52/B40)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>8410.75</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>28.51</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4177,15 +4191,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$59,D41,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$59,D41,$C$2:$C$59,C41)+1)/2)/COUNTIFS($D$2:$D$59,D41,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4193,25 +4207,25 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="30">
         <f>IFERROR(B45/B41-1,"")</f>
         <v/>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="30">
         <f>IFERROR((B53/B41)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>8183.75</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>22.24</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4219,15 +4233,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$59,D42,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$59,D42,$C$2:$C$59,C42)+1)/2)/COUNTIFS($D$2:$D$59,D42,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4235,25 +4249,25 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="30">
         <f>IFERROR(B46/B42-1,"")</f>
         <v/>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="30">
         <f>IFERROR((B54/B42)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>7297.65</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>18.44</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4261,15 +4275,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$59,D43,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$59,D43,$C$2:$C$59,C43)+1)/2)/COUNTIFS($D$2:$D$59,D43,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4277,25 +4291,25 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="30">
         <f>IFERROR(B47/B43-1,"")</f>
         <v/>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="30">
         <f>IFERROR((B55/B43)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>8332.700000000001</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>21.71</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4303,15 +4317,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$59,D44,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$59,D44,$C$2:$C$59,C44)+1)/2)/COUNTIFS($D$2:$D$59,D44,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4319,25 +4333,25 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="30">
         <f>IFERROR(B48/B44-1,"")</f>
         <v/>
       </c>
-      <c r="J44" s="16">
+      <c r="J44" s="30">
         <f>IFERROR((B56/B44)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>8751.75</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>24.3</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4345,15 +4359,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E45" s="21">
+      <c r="E45" s="33">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="30">
         <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
         <v/>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="30">
         <f>IF(C45="","",(COUNTIFS($D$2:$D$59,D45,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$59,D45,$C$2:$C$59,C45)+1)/2)/COUNTIFS($D$2:$D$59,D45,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4361,25 +4375,25 @@
         <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="30">
         <f>IFERROR(B49/B45-1,"")</f>
         <v/>
       </c>
-      <c r="J45" s="16">
+      <c r="J45" s="30">
         <f>IFERROR((B57/B45)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K45" s="16" t="n"/>
-      <c r="L45" s="16" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>8466.799999999999</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>21.63</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4387,15 +4401,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="33">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="30">
         <f>IF(AND(D46=D42,E42&lt;&gt;""),E46/E42-1,"")</f>
         <v/>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="30">
         <f>IF(C46="","",(COUNTIFS($D$2:$D$59,D46,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C46)+(COUNTIFS($D$2:$D$59,D46,$C$2:$C$59,C46)+1)/2)/COUNTIFS($D$2:$D$59,D46,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4403,25 +4417,25 @@
         <f>IF(G46="","",IF(G46&lt;=20%,"Q1 Cheapest",IF(G46&lt;=40%,"Q2",IF(G46&lt;=60%,"Q3",IF(G46&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="30">
         <f>IFERROR(B50/B46-1,"")</f>
         <v/>
       </c>
-      <c r="J46" s="16">
+      <c r="J46" s="30">
         <f>IFERROR((B58/B46)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K46" s="16" t="n"/>
-      <c r="L46" s="16" t="n"/>
+      <c r="K46" s="30" t="n"/>
+      <c r="L46" s="30" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>10126.85</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>24.03</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4429,15 +4443,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="33">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="30">
         <f>IF(AND(D47=D43,E43&lt;&gt;""),E47/E43-1,"")</f>
         <v/>
       </c>
-      <c r="G47" s="16">
+      <c r="G47" s="30">
         <f>IF(C47="","",(COUNTIFS($D$2:$D$59,D47,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C47)+(COUNTIFS($D$2:$D$59,D47,$C$2:$C$59,C47)+1)/2)/COUNTIFS($D$2:$D$59,D47,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4445,25 +4459,25 @@
         <f>IF(G47="","",IF(G47&lt;=20%,"Q1 Cheapest",IF(G47&lt;=40%,"Q2",IF(G47&lt;=60%,"Q3",IF(G47&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I47" s="16">
+      <c r="I47" s="30">
         <f>IFERROR(B51/B47-1,"")</f>
         <v/>
       </c>
-      <c r="J47" s="16">
+      <c r="J47" s="30">
         <f>IFERROR((B59/B47)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K47" s="16" t="n"/>
-      <c r="L47" s="16" t="n"/>
+      <c r="K47" s="30" t="n"/>
+      <c r="L47" s="30" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>11611.65</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>21.99</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4471,15 +4485,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E48" s="21">
+      <c r="E48" s="33">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="30">
         <f>IF(AND(D48=D44,E44&lt;&gt;""),E48/E44-1,"")</f>
         <v/>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="30">
         <f>IF(C48="","",(COUNTIFS($D$2:$D$59,D48,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C48)+(COUNTIFS($D$2:$D$59,D48,$C$2:$C$59,C48)+1)/2)/COUNTIFS($D$2:$D$59,D48,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4487,22 +4501,22 @@
         <f>IF(G48="","",IF(G48&lt;=20%,"Q1 Cheapest",IF(G48&lt;=40%,"Q2",IF(G48&lt;=60%,"Q3",IF(G48&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="30">
         <f>IFERROR(B52/B48-1,"")</f>
         <v/>
       </c>
-      <c r="J48" s="16" t="n"/>
-      <c r="K48" s="16" t="n"/>
-      <c r="L48" s="16" t="n"/>
+      <c r="J48" s="30" t="n"/>
+      <c r="K48" s="30" t="n"/>
+      <c r="L48" s="30" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>13144.95</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>21.41</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -4510,15 +4524,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E49" s="21">
+      <c r="E49" s="33">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="30">
         <f>IF(AND(D49=D45,E45&lt;&gt;""),E49/E45-1,"")</f>
         <v/>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="30">
         <f>IF(C49="","",(COUNTIFS($D$2:$D$59,D49,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C49)+(COUNTIFS($D$2:$D$59,D49,$C$2:$C$59,C49)+1)/2)/COUNTIFS($D$2:$D$59,D49,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4526,22 +4540,22 @@
         <f>IF(G49="","",IF(G49&lt;=20%,"Q1 Cheapest",IF(G49&lt;=40%,"Q2",IF(G49&lt;=60%,"Q3",IF(G49&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="30">
         <f>IFERROR(B53/B49-1,"")</f>
         <v/>
       </c>
-      <c r="J49" s="16" t="n"/>
-      <c r="K49" s="16" t="n"/>
-      <c r="L49" s="16" t="n"/>
+      <c r="J49" s="30" t="n"/>
+      <c r="K49" s="30" t="n"/>
+      <c r="L49" s="30" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>13526.5</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>33.17</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4549,15 +4563,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="33">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="30">
         <f>IF(AND(D50=D46,E46&lt;&gt;""),E50/E46-1,"")</f>
         <v/>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="30">
         <f>IF(C50="","",(COUNTIFS($D$2:$D$59,D50,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C50)+(COUNTIFS($D$2:$D$59,D50,$C$2:$C$59,C50)+1)/2)/COUNTIFS($D$2:$D$59,D50,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4565,22 +4579,22 @@
         <f>IF(G50="","",IF(G50&lt;=20%,"Q1 Cheapest",IF(G50&lt;=40%,"Q2",IF(G50&lt;=60%,"Q3",IF(G50&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="30">
         <f>IFERROR(B54/B50-1,"")</f>
         <v/>
       </c>
-      <c r="J50" s="16" t="n"/>
-      <c r="K50" s="16" t="n"/>
-      <c r="L50" s="16" t="n"/>
+      <c r="J50" s="30" t="n"/>
+      <c r="K50" s="30" t="n"/>
+      <c r="L50" s="30" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>15711.15</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>44.27</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4588,15 +4602,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E51" s="21">
+      <c r="E51" s="33">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="30">
         <f>IF(AND(D51=D47,E47&lt;&gt;""),E51/E47-1,"")</f>
         <v/>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="30">
         <f>IF(C51="","",(COUNTIFS($D$2:$D$59,D51,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C51)+(COUNTIFS($D$2:$D$59,D51,$C$2:$C$59,C51)+1)/2)/COUNTIFS($D$2:$D$59,D51,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4604,22 +4618,22 @@
         <f>IF(G51="","",IF(G51&lt;=20%,"Q1 Cheapest",IF(G51&lt;=40%,"Q2",IF(G51&lt;=60%,"Q3",IF(G51&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="30">
         <f>IFERROR(B55/B51-1,"")</f>
         <v/>
       </c>
-      <c r="J51" s="16" t="n"/>
-      <c r="K51" s="16" t="n"/>
-      <c r="L51" s="16" t="n"/>
+      <c r="J51" s="30" t="n"/>
+      <c r="K51" s="30" t="n"/>
+      <c r="L51" s="30" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>16883.35</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>50.95</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4627,15 +4641,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="33">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="30">
         <f>IF(AND(D52=D48,E48&lt;&gt;""),E52/E48-1,"")</f>
         <v/>
       </c>
-      <c r="G52" s="16">
+      <c r="G52" s="30">
         <f>IF(C52="","",(COUNTIFS($D$2:$D$59,D52,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C52)+(COUNTIFS($D$2:$D$59,D52,$C$2:$C$59,C52)+1)/2)/COUNTIFS($D$2:$D$59,D52,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4643,22 +4657,22 @@
         <f>IF(G52="","",IF(G52&lt;=20%,"Q1 Cheapest",IF(G52&lt;=40%,"Q2",IF(G52&lt;=60%,"Q3",IF(G52&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="30">
         <f>IFERROR(B56/B52-1,"")</f>
         <v/>
       </c>
-      <c r="J52" s="16" t="n"/>
-      <c r="K52" s="16" t="n"/>
-      <c r="L52" s="16" t="n"/>
+      <c r="J52" s="30" t="n"/>
+      <c r="K52" s="30" t="n"/>
+      <c r="L52" s="30" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>15974.1</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>50</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4666,15 +4680,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E53" s="21">
+      <c r="E53" s="33">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="30">
         <f>IF(AND(D53=D49,E49&lt;&gt;""),E53/E49-1,"")</f>
         <v/>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="30">
         <f>IF(C53="","",(COUNTIFS($D$2:$D$59,D53,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C53)+(COUNTIFS($D$2:$D$59,D53,$C$2:$C$59,C53)+1)/2)/COUNTIFS($D$2:$D$59,D53,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4682,22 +4696,22 @@
         <f>IF(G53="","",IF(G53&lt;=20%,"Q1 Cheapest",IF(G53&lt;=40%,"Q2",IF(G53&lt;=60%,"Q3",IF(G53&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="30">
         <f>IFERROR(B57/B53-1,"")</f>
         <v/>
       </c>
-      <c r="J53" s="16" t="n"/>
-      <c r="K53" s="16" t="n"/>
-      <c r="L53" s="16" t="n"/>
+      <c r="J53" s="30" t="n"/>
+      <c r="K53" s="30" t="n"/>
+      <c r="L53" s="30" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>14561.6</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>39.22</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4705,15 +4719,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E54" s="21">
+      <c r="E54" s="33">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="30">
         <f>IF(AND(D54=D50,E50&lt;&gt;""),E54/E50-1,"")</f>
         <v/>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="30">
         <f>IF(C54="","",(COUNTIFS($D$2:$D$59,D54,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C54)+(COUNTIFS($D$2:$D$59,D54,$C$2:$C$59,C54)+1)/2)/COUNTIFS($D$2:$D$59,D54,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4721,22 +4735,22 @@
         <f>IF(G54="","",IF(G54&lt;=20%,"Q1 Cheapest",IF(G54&lt;=40%,"Q2",IF(G54&lt;=60%,"Q3",IF(G54&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I54" s="16">
+      <c r="I54" s="30">
         <f>IFERROR(B58/B54-1,"")</f>
         <v/>
       </c>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="16" t="n"/>
+      <c r="J54" s="30" t="n"/>
+      <c r="K54" s="30" t="n"/>
+      <c r="L54" s="30" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>16846.2</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>40.48</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4744,15 +4758,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E55" s="21">
+      <c r="E55" s="33">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="30">
         <f>IF(AND(D55=D51,E51&lt;&gt;""),E55/E51-1,"")</f>
         <v/>
       </c>
-      <c r="G55" s="16">
+      <c r="G55" s="30">
         <f>IF(C55="","",(COUNTIFS($D$2:$D$59,D55,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C55)+(COUNTIFS($D$2:$D$59,D55,$C$2:$C$59,C55)+1)/2)/COUNTIFS($D$2:$D$59,D55,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4760,22 +4774,22 @@
         <f>IF(G55="","",IF(G55&lt;=20%,"Q1 Cheapest",IF(G55&lt;=40%,"Q2",IF(G55&lt;=60%,"Q3",IF(G55&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I55" s="16">
+      <c r="I55" s="30">
         <f>IFERROR(B59/B55-1,"")</f>
         <v/>
       </c>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="16" t="n"/>
+      <c r="J55" s="30" t="n"/>
+      <c r="K55" s="30" t="n"/>
+      <c r="L55" s="30" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>15945.4</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>32.97</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4783,15 +4797,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="33">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="30">
         <f>IF(AND(D56=D52,E52&lt;&gt;""),E56/E52-1,"")</f>
         <v/>
       </c>
-      <c r="G56" s="16">
+      <c r="G56" s="30">
         <f>IF(C56="","",(COUNTIFS($D$2:$D$59,D56,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C56)+(COUNTIFS($D$2:$D$59,D56,$C$2:$C$59,C56)+1)/2)/COUNTIFS($D$2:$D$59,D56,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4799,19 +4813,19 @@
         <f>IF(G56="","",IF(G56&lt;=20%,"Q1 Cheapest",IF(G56&lt;=40%,"Q2",IF(G56&lt;=60%,"Q3",IF(G56&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I56" s="16" t="n"/>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="16" t="n"/>
+      <c r="I56" s="30" t="n"/>
+      <c r="J56" s="30" t="n"/>
+      <c r="K56" s="30" t="n"/>
+      <c r="L56" s="30" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>17254.05</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>33.72</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4819,15 +4833,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E57" s="21">
+      <c r="E57" s="33">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="30">
         <f>IF(AND(D57=D53,E53&lt;&gt;""),E57/E53-1,"")</f>
         <v/>
       </c>
-      <c r="G57" s="16">
+      <c r="G57" s="30">
         <f>IF(C57="","",(COUNTIFS($D$2:$D$59,D57,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C57)+(COUNTIFS($D$2:$D$59,D57,$C$2:$C$59,C57)+1)/2)/COUNTIFS($D$2:$D$59,D57,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4835,19 +4849,19 @@
         <f>IF(G57="","",IF(G57&lt;=20%,"Q1 Cheapest",IF(G57&lt;=40%,"Q2",IF(G57&lt;=60%,"Q3",IF(G57&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I57" s="16" t="n"/>
-      <c r="J57" s="16" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="16" t="n"/>
+      <c r="I57" s="30" t="n"/>
+      <c r="J57" s="30" t="n"/>
+      <c r="K57" s="30" t="n"/>
+      <c r="L57" s="30" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>14983.35</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>32.13</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4855,15 +4869,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E58" s="21">
+      <c r="E58" s="33">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="30">
         <f>IF(AND(D58=D54,E54&lt;&gt;""),E58/E54-1,"")</f>
         <v/>
       </c>
-      <c r="G58" s="16">
+      <c r="G58" s="30">
         <f>IF(C58="","",(COUNTIFS($D$2:$D$59,D58,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C58)+(COUNTIFS($D$2:$D$59,D58,$C$2:$C$59,C58)+1)/2)/COUNTIFS($D$2:$D$59,D58,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4871,19 +4885,19 @@
         <f>IF(G58="","",IF(G58&lt;=20%,"Q1 Cheapest",IF(G58&lt;=40%,"Q2",IF(G58&lt;=60%,"Q3",IF(G58&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I58" s="16" t="n"/>
-      <c r="J58" s="16" t="n"/>
-      <c r="K58" s="16" t="n"/>
-      <c r="L58" s="16" t="n"/>
+      <c r="I58" s="30" t="n"/>
+      <c r="J58" s="30" t="n"/>
+      <c r="K58" s="30" t="n"/>
+      <c r="L58" s="30" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>17594.9</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>32.87</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4891,15 +4905,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E59" s="21">
+      <c r="E59" s="33">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="30">
         <f>IF(AND(D59=D55,E55&lt;&gt;""),E59/E55-1,"")</f>
         <v/>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="30">
         <f>IF(C59="","",(COUNTIFS($D$2:$D$59,D59,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C59)+(COUNTIFS($D$2:$D$59,D59,$C$2:$C$59,C59)+1)/2)/COUNTIFS($D$2:$D$59,D59,$C$2:$C$59,"&gt;0"))</f>
         <v/>
       </c>
@@ -4907,10 +4921,10 @@
         <f>IF(G59="","",IF(G59&lt;=20%,"Q1 Cheapest",IF(G59&lt;=40%,"Q2",IF(G59&lt;=60%,"Q3",IF(G59&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I59" s="16" t="n"/>
-      <c r="J59" s="16" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="16" t="n"/>
+      <c r="I59" s="30" t="n"/>
+      <c r="J59" s="30" t="n"/>
+      <c r="K59" s="30" t="n"/>
+      <c r="L59" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4987,30 +5001,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>17882.9</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>35.17</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.689393939394</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.142760179357</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -5020,30 +5034,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>17879.65</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>35.16</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.689393939394</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.143066575201</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -5053,30 +5067,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>17878.6</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>35.16</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.689393939394</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.142853025034</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -5196,4 +5210,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5109,6 +5112,1112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Midcap 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alkem Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>APL Apollo Tubes Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ashok Leyland Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AU Small Finance Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bharat Forge Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BSE Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coforge Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Colgate Palmolive (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dabur India Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dixon Technologies (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Federal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FSN E-Commerce Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GMR Airports Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Godrej Properties Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Havells India Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IDFC First Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Indus Towers Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IndusInd Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Info Edge (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Laurus Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mankind Pharma Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Marico Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Max Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MphasiS Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Multi Commodity Exchange of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NHPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NMDC Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Oil India Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>One 97 Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PB Fintech Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Persistent Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Phoenix Mills Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prestige Estates Projects Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SBI Cards and Payment Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SRF Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supreme Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Suzlon Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Swiggy Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SWIGGY</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tube Investments of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>UPL Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Waaree Energies Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Yes Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -5210,43 +6319,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Midcap 50 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17878.6</v>
+        <v>17979.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.16</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6893939393939394</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>508.4926052332196</v>
+        <v>508.4742647058824</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1428530250344324</v>
+        <v>0.1427669899968771</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02844141069397042</v>
+        <v>0.02828054298642534</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>31.06060606060606</v>
+        <v>29.54545454545454</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>77.14121001377296</v>
+        <v>77.10679599875084</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>44.88478724655613</v>
+        <v>43.81385698144343</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.16212101032164</v>
+        <v>24.15953258476319</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12286.25986049876</v>
+        <v>12284.50056667527</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.3127951931080307</v>
+        <v>-0.316755300204661</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.52560635403756</v>
+        <v>37.51908735633481</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19081.49333792082</v>
+        <v>19077.49035594811</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.0672811818554484</v>
+        <v>0.061060162792274</v>
       </c>
     </row>
     <row r="16">
@@ -4942,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5099,6 +5099,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>17979.65</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.7045454545449999</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.142766989997</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17979.65</v>
+        <v>17518.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>35.36</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.7045454545454546</v>
+        <v>0.6742424242424242</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>508.4742647058824</v>
+        <v>508.5065312046444</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1427669899968771</v>
+        <v>0.1430195080391885</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02828054298642534</v>
+        <v>0.02902757619738752</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>29.54545454545454</v>
+        <v>32.57575757575758</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>77.10679599875084</v>
+        <v>77.2078032156754</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>43.81385698144343</v>
+        <v>45.96537126773292</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.15953258476319</v>
+        <v>24.16712977043615</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12284.50056667527</v>
+        <v>12289.14332873698</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.316755300204661</v>
+        <v>-0.2984867991165122</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.51908735633481</v>
+        <v>37.53822100914079</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19077.49035594811</v>
+        <v>19088.43055295149</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.061060162792274</v>
+        <v>0.08964357065720741</v>
       </c>
     </row>
     <row r="16">
@@ -4942,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5132,6 +5132,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>17518.05</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.674242424242</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.143019508039</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5172,7 +5205,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17518.05</v>
+        <v>17474.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.45</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>508.5065312046444</v>
+        <v>508.4114052953157</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1430195080391885</v>
+        <v>0.1426068169373322</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02902757619738752</v>
+        <v>0.02909514111143439</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>77.2078032156754</v>
+        <v>77.04272677493289</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.96537126773292</v>
+        <v>45.91584833551017</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.16712977043615</v>
+        <v>24.15471366385745</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12289.14332873698</v>
+        <v>12280.53191834773</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2984867991165122</v>
+        <v>-0.297215197443775</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.53822100914079</v>
+        <v>37.50695081479442</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19088.43055295149</v>
+        <v>19068.96157209192</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.08964357065720741</v>
+        <v>0.09127002661607286</v>
       </c>
     </row>
     <row r="16">
@@ -4942,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5165,6 +5165,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>17474.1</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.674242424242</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.142606816937</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5205,7 +5238,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17474.1</v>
+        <v>17208.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>34.37</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6742424242424242</v>
+        <v>0.6287878787878788</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>508.4114052953157</v>
+        <v>508.5372340425532</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1426068169373322</v>
+        <v>0.1429240263786278</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02909514111143439</v>
+        <v>0.02955082742316785</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>32.57575757575758</v>
+        <v>37.12121212121212</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>77.04272677493289</v>
+        <v>77.16961055145111</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>45.91584833551017</v>
+        <v>49.13573165028382</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.15471366385745</v>
+        <v>24.164257136477</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12280.53191834773</v>
+        <v>12288.42448687704</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.297215197443775</v>
+        <v>-0.285926207550916</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.50695081479442</v>
+        <v>37.53098622731774</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19068.96157209192</v>
+        <v>19085.90392692932</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.09127002661607286</v>
+        <v>0.1090716970247558</v>
       </c>
     </row>
     <row r="16">
@@ -4942,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5198,6 +5198,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>17208.9</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.628787878788</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.142924026379</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5238,7 +5271,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17208.9</v>
+        <v>17030.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>33.84</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6287878787878788</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>508.5372340425532</v>
+        <v>508.5264257987458</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1429240263786278</v>
+        <v>0.1430891968501962</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02955082742316785</v>
+        <v>0.02985965959988056</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>37.12121212121212</v>
+        <v>38.63636363636363</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>77.16961055145111</v>
+        <v>77.23567874007847</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>49.13573165028382</v>
+        <v>50.21615816747808</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.164257136477</v>
+        <v>24.16922640809305</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12288.42448687704</v>
+        <v>12290.69031962822</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.285926207550916</v>
+        <v>-0.2783151266618977</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.53098622731774</v>
+        <v>37.54350142990629</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19085.90392692932</v>
+        <v>19091.86259412035</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1090716970247558</v>
+        <v>0.121036172884631</v>
       </c>
     </row>
     <row r="16">
@@ -4942,7 +4942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5231,6 +5231,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>17030.55</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.613636363636</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.14308919685</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5271,7 +5304,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5341,17 +5374,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5361,12 +5394,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5381,17 +5414,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5401,17 +5434,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5421,17 +5454,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5441,17 +5474,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5461,17 +5494,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Dabur India Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5481,17 +5514,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5501,17 +5534,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5521,17 +5554,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5541,17 +5574,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dabur India Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5561,17 +5594,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>GE Vernova T&amp;D India Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5581,17 +5614,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5601,17 +5634,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>GMR Airports Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5654,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>Godrej Properties Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5641,17 +5674,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GMR Airports Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5694,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godrej Properties Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5681,17 +5714,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Havells India Ltd.</t>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5701,17 +5734,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5721,17 +5754,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hindustan Petroleum Corporation Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5741,17 +5774,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5761,17 +5794,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5781,17 +5814,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5801,17 +5834,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>Info Edge (India) Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5821,17 +5854,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd.</t>
+          <t>JSW Energy Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -5941,17 +5974,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MphasiS Ltd.</t>
+          <t>Multi Commodity Exchange of India Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5961,17 +5994,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6121,17 +6154,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>Prestige Estates Projects Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -6141,17 +6174,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Prestige Estates Projects Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6161,17 +6194,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>SRF Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6181,17 +6214,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>Suzlon Energy Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6201,17 +6234,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Swiggy Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6221,17 +6254,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Suzlon Energy Ltd.</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6241,17 +6274,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Swiggy Ltd.</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6261,17 +6294,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6281,17 +6314,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>Vishal Mega Mart Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -568,10 +568,10 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17030.55</v>
+        <v>17028.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>33.49</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.6136363636363636</v>
+        <v>0.4477611940298508</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>508.5264257987458</v>
+        <v>564.9867285998673</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1430891968501962</v>
+        <v>0.1682123021020248</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.02985965959988056</v>
+        <v>0.033178500331785</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>38.63636363636363</v>
+        <v>55.22388059701493</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>77.23567874007847</v>
+        <v>83.64246042040496</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>50.21615816747808</v>
+        <v>63.74945454403193</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.16922640809305</v>
+        <v>24.59541878016918</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>12290.69031962822</v>
+        <v>13896.08519515153</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.2783151266618977</v>
+        <v>-0.1839608898417657</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>37.54350142990629</v>
+        <v>38.00778326647087</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>19091.86259412035</v>
+        <v>21473.89312905616</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.121036172884631</v>
+        <v>0.2610412497170163</v>
       </c>
     </row>
     <row r="16">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.03458683366427362</v>
+        <v>0.0375650929609006</v>
       </c>
       <c r="D19" s="30" t="n">
         <v>0.1641163300520954</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.05128555869590079</v>
+        <v>0.06719038760344531</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1982429041594077</v>
+        <v>0.151179001200638</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.1496483806058929</v>
@@ -887,22 +887,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.07652386056999227</v>
+        <v>0.06793808872778362</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>0.1173100602015256</v>
+        <v>0.1307418222863642</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>0.1643476874521761</v>
+        <v>0.1616418994348091</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>0.1754930481859425</v>
+        <v>0.1662719807498725</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="22">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
@@ -975,7 +975,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2294,6 +2294,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>17028.7</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2310,7 +2329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2410,7 +2429,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$59,D2,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$59,D2,$C$2:$C$59,C2)+1)/2)/COUNTIFS($D$2:$D$59,D2,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$60,D2,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$60,D2,$C$2:$C$60,C2)+1)/2)/COUNTIFS($D$2:$D$60,D2,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2455,7 +2474,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$59,D3,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$59,D3,$C$2:$C$59,C3)+1)/2)/COUNTIFS($D$2:$D$59,D3,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$60,D3,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$60,D3,$C$2:$C$60,C3)+1)/2)/COUNTIFS($D$2:$D$60,D3,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2500,7 +2519,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$59,D4,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$59,D4,$C$2:$C$59,C4)+1)/2)/COUNTIFS($D$2:$D$59,D4,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$60,D4,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$60,D4,$C$2:$C$60,C4)+1)/2)/COUNTIFS($D$2:$D$60,D4,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2545,7 +2564,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$59,D5,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$59,D5,$C$2:$C$59,C5)+1)/2)/COUNTIFS($D$2:$D$59,D5,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$60,D5,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$60,D5,$C$2:$C$60,C5)+1)/2)/COUNTIFS($D$2:$D$60,D5,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2593,7 +2612,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$59,D6,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$59,D6,$C$2:$C$59,C6)+1)/2)/COUNTIFS($D$2:$D$59,D6,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$60,D6,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$60,D6,$C$2:$C$60,C6)+1)/2)/COUNTIFS($D$2:$D$60,D6,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2641,7 +2660,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$59,D7,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$59,D7,$C$2:$C$59,C7)+1)/2)/COUNTIFS($D$2:$D$59,D7,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$60,D7,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$60,D7,$C$2:$C$60,C7)+1)/2)/COUNTIFS($D$2:$D$60,D7,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2689,7 +2708,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$59,D8,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$59,D8,$C$2:$C$59,C8)+1)/2)/COUNTIFS($D$2:$D$59,D8,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$60,D8,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$60,D8,$C$2:$C$60,C8)+1)/2)/COUNTIFS($D$2:$D$60,D8,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2737,7 +2756,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$59,D9,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$59,D9,$C$2:$C$59,C9)+1)/2)/COUNTIFS($D$2:$D$59,D9,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$60,D9,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$60,D9,$C$2:$C$60,C9)+1)/2)/COUNTIFS($D$2:$D$60,D9,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2785,7 +2804,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$59,D10,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$59,D10,$C$2:$C$59,C10)+1)/2)/COUNTIFS($D$2:$D$59,D10,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$60,D10,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$60,D10,$C$2:$C$60,C10)+1)/2)/COUNTIFS($D$2:$D$60,D10,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2833,7 +2852,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$59,D11,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$59,D11,$C$2:$C$59,C11)+1)/2)/COUNTIFS($D$2:$D$59,D11,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$60,D11,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$60,D11,$C$2:$C$60,C11)+1)/2)/COUNTIFS($D$2:$D$60,D11,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2881,7 +2900,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$59,D12,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$59,D12,$C$2:$C$59,C12)+1)/2)/COUNTIFS($D$2:$D$59,D12,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$60,D12,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$60,D12,$C$2:$C$60,C12)+1)/2)/COUNTIFS($D$2:$D$60,D12,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2929,7 +2948,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$59,D13,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$59,D13,$C$2:$C$59,C13)+1)/2)/COUNTIFS($D$2:$D$59,D13,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$60,D13,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$60,D13,$C$2:$C$60,C13)+1)/2)/COUNTIFS($D$2:$D$60,D13,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2977,7 +2996,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$59,D14,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$59,D14,$C$2:$C$59,C14)+1)/2)/COUNTIFS($D$2:$D$59,D14,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$60,D14,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$60,D14,$C$2:$C$60,C14)+1)/2)/COUNTIFS($D$2:$D$60,D14,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -3025,7 +3044,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$59,D15,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$59,D15,$C$2:$C$59,C15)+1)/2)/COUNTIFS($D$2:$D$59,D15,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$60,D15,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$60,D15,$C$2:$C$60,C15)+1)/2)/COUNTIFS($D$2:$D$60,D15,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3073,7 +3092,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$59,D16,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$59,D16,$C$2:$C$59,C16)+1)/2)/COUNTIFS($D$2:$D$59,D16,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$60,D16,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$60,D16,$C$2:$C$60,C16)+1)/2)/COUNTIFS($D$2:$D$60,D16,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3121,7 +3140,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$59,D17,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$59,D17,$C$2:$C$59,C17)+1)/2)/COUNTIFS($D$2:$D$59,D17,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$60,D17,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$60,D17,$C$2:$C$60,C17)+1)/2)/COUNTIFS($D$2:$D$60,D17,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3169,7 +3188,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$59,D18,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$59,D18,$C$2:$C$59,C18)+1)/2)/COUNTIFS($D$2:$D$59,D18,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$60,D18,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$60,D18,$C$2:$C$60,C18)+1)/2)/COUNTIFS($D$2:$D$60,D18,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3217,7 +3236,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$59,D19,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$59,D19,$C$2:$C$59,C19)+1)/2)/COUNTIFS($D$2:$D$59,D19,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$60,D19,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$60,D19,$C$2:$C$60,C19)+1)/2)/COUNTIFS($D$2:$D$60,D19,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3265,7 +3284,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$59,D20,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$59,D20,$C$2:$C$59,C20)+1)/2)/COUNTIFS($D$2:$D$59,D20,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$60,D20,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$60,D20,$C$2:$C$60,C20)+1)/2)/COUNTIFS($D$2:$D$60,D20,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3284,7 +3303,10 @@
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="30" t="n"/>
+      <c r="L20" s="30">
+        <f>IFERROR((B60/B20)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="n">
@@ -3310,7 +3332,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$59,D21,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$59,D21,$C$2:$C$59,C21)+1)/2)/COUNTIFS($D$2:$D$59,D21,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$60,D21,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$60,D21,$C$2:$C$60,C21)+1)/2)/COUNTIFS($D$2:$D$60,D21,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3355,7 +3377,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$59,D22,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$59,D22,$C$2:$C$59,C22)+1)/2)/COUNTIFS($D$2:$D$59,D22,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$60,D22,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$60,D22,$C$2:$C$60,C22)+1)/2)/COUNTIFS($D$2:$D$60,D22,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3400,7 +3422,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$59,D23,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$59,D23,$C$2:$C$59,C23)+1)/2)/COUNTIFS($D$2:$D$59,D23,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$60,D23,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$60,D23,$C$2:$C$60,C23)+1)/2)/COUNTIFS($D$2:$D$60,D23,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3445,7 +3467,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$59,D24,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$59,D24,$C$2:$C$59,C24)+1)/2)/COUNTIFS($D$2:$D$59,D24,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$60,D24,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$60,D24,$C$2:$C$60,C24)+1)/2)/COUNTIFS($D$2:$D$60,D24,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3490,7 +3512,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$59,D25,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$59,D25,$C$2:$C$59,C25)+1)/2)/COUNTIFS($D$2:$D$59,D25,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$60,D25,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$60,D25,$C$2:$C$60,C25)+1)/2)/COUNTIFS($D$2:$D$60,D25,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3535,7 +3557,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$59,D26,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$59,D26,$C$2:$C$59,C26)+1)/2)/COUNTIFS($D$2:$D$59,D26,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$60,D26,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$60,D26,$C$2:$C$60,C26)+1)/2)/COUNTIFS($D$2:$D$60,D26,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3580,7 +3602,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$59,D27,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$59,D27,$C$2:$C$59,C27)+1)/2)/COUNTIFS($D$2:$D$59,D27,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$60,D27,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$60,D27,$C$2:$C$60,C27)+1)/2)/COUNTIFS($D$2:$D$60,D27,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3625,7 +3647,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$59,D28,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$59,D28,$C$2:$C$59,C28)+1)/2)/COUNTIFS($D$2:$D$59,D28,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$60,D28,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$60,D28,$C$2:$C$60,C28)+1)/2)/COUNTIFS($D$2:$D$60,D28,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3670,7 +3692,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$59,D29,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$59,D29,$C$2:$C$59,C29)+1)/2)/COUNTIFS($D$2:$D$59,D29,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$60,D29,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$60,D29,$C$2:$C$60,C29)+1)/2)/COUNTIFS($D$2:$D$60,D29,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3715,7 +3737,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$59,D30,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$59,D30,$C$2:$C$59,C30)+1)/2)/COUNTIFS($D$2:$D$59,D30,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$60,D30,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$60,D30,$C$2:$C$60,C30)+1)/2)/COUNTIFS($D$2:$D$60,D30,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3760,7 +3782,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$59,D31,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$59,D31,$C$2:$C$59,C31)+1)/2)/COUNTIFS($D$2:$D$59,D31,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$60,D31,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$60,D31,$C$2:$C$60,C31)+1)/2)/COUNTIFS($D$2:$D$60,D31,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3805,7 +3827,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$59,D32,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$59,D32,$C$2:$C$59,C32)+1)/2)/COUNTIFS($D$2:$D$59,D32,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$60,D32,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$60,D32,$C$2:$C$60,C32)+1)/2)/COUNTIFS($D$2:$D$60,D32,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3850,7 +3872,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$59,D33,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$59,D33,$C$2:$C$59,C33)+1)/2)/COUNTIFS($D$2:$D$59,D33,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$60,D33,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$60,D33,$C$2:$C$60,C33)+1)/2)/COUNTIFS($D$2:$D$60,D33,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3895,7 +3917,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$59,D34,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$59,D34,$C$2:$C$59,C34)+1)/2)/COUNTIFS($D$2:$D$59,D34,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$60,D34,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$60,D34,$C$2:$C$60,C34)+1)/2)/COUNTIFS($D$2:$D$60,D34,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3938,7 +3960,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$59,D35,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$59,D35,$C$2:$C$59,C35)+1)/2)/COUNTIFS($D$2:$D$59,D35,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$60,D35,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$60,D35,$C$2:$C$60,C35)+1)/2)/COUNTIFS($D$2:$D$60,D35,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3981,7 +4003,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$59,D36,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$59,D36,$C$2:$C$59,C36)+1)/2)/COUNTIFS($D$2:$D$59,D36,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$60,D36,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$60,D36,$C$2:$C$60,C36)+1)/2)/COUNTIFS($D$2:$D$60,D36,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -4026,7 +4048,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$59,D37,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$59,D37,$C$2:$C$59,C37)+1)/2)/COUNTIFS($D$2:$D$59,D37,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$60,D37,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$60,D37,$C$2:$C$60,C37)+1)/2)/COUNTIFS($D$2:$D$60,D37,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -4071,7 +4093,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$59,D38,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$59,D38,$C$2:$C$59,C38)+1)/2)/COUNTIFS($D$2:$D$59,D38,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$60,D38,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$60,D38,$C$2:$C$60,C38)+1)/2)/COUNTIFS($D$2:$D$60,D38,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4116,7 +4138,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$59,D39,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$59,D39,$C$2:$C$59,C39)+1)/2)/COUNTIFS($D$2:$D$59,D39,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$60,D39,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$60,D39,$C$2:$C$60,C39)+1)/2)/COUNTIFS($D$2:$D$60,D39,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4161,7 +4183,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$59,D40,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$59,D40,$C$2:$C$59,C40)+1)/2)/COUNTIFS($D$2:$D$59,D40,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$60,D40,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$60,D40,$C$2:$C$60,C40)+1)/2)/COUNTIFS($D$2:$D$60,D40,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4176,7 +4198,10 @@
         <f>IFERROR((B52/B40)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K40" s="30" t="n"/>
+      <c r="K40" s="30">
+        <f>IFERROR((B60/B40)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
@@ -4203,7 +4228,7 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$59,D41,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$59,D41,$C$2:$C$59,C41)+1)/2)/COUNTIFS($D$2:$D$59,D41,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$60,D41,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$60,D41,$C$2:$C$60,C41)+1)/2)/COUNTIFS($D$2:$D$60,D41,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
@@ -4245,7 +4270,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$59,D42,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$59,D42,$C$2:$C$59,C42)+1)/2)/COUNTIFS($D$2:$D$59,D42,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$60,D42,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$60,D42,$C$2:$C$60,C42)+1)/2)/COUNTIFS($D$2:$D$60,D42,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4287,7 +4312,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$59,D43,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$59,D43,$C$2:$C$59,C43)+1)/2)/COUNTIFS($D$2:$D$59,D43,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$60,D43,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$60,D43,$C$2:$C$60,C43)+1)/2)/COUNTIFS($D$2:$D$60,D43,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4329,7 +4354,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$59,D44,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$59,D44,$C$2:$C$59,C44)+1)/2)/COUNTIFS($D$2:$D$59,D44,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$60,D44,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$60,D44,$C$2:$C$60,C44)+1)/2)/COUNTIFS($D$2:$D$60,D44,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4371,7 +4396,7 @@
         <v/>
       </c>
       <c r="G45" s="30">
-        <f>IF(C45="","",(COUNTIFS($D$2:$D$59,D45,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$59,D45,$C$2:$C$59,C45)+1)/2)/COUNTIFS($D$2:$D$59,D45,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$60,D45,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$60,D45,$C$2:$C$60,C45)+1)/2)/COUNTIFS($D$2:$D$60,D45,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H45">
@@ -4413,7 +4438,7 @@
         <v/>
       </c>
       <c r="G46" s="30">
-        <f>IF(C46="","",(COUNTIFS($D$2:$D$59,D46,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C46)+(COUNTIFS($D$2:$D$59,D46,$C$2:$C$59,C46)+1)/2)/COUNTIFS($D$2:$D$59,D46,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C46="","",(COUNTIFS($D$2:$D$60,D46,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C46)+(COUNTIFS($D$2:$D$60,D46,$C$2:$C$60,C46)+1)/2)/COUNTIFS($D$2:$D$60,D46,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H46">
@@ -4455,7 +4480,7 @@
         <v/>
       </c>
       <c r="G47" s="30">
-        <f>IF(C47="","",(COUNTIFS($D$2:$D$59,D47,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C47)+(COUNTIFS($D$2:$D$59,D47,$C$2:$C$59,C47)+1)/2)/COUNTIFS($D$2:$D$59,D47,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C47="","",(COUNTIFS($D$2:$D$60,D47,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C47)+(COUNTIFS($D$2:$D$60,D47,$C$2:$C$60,C47)+1)/2)/COUNTIFS($D$2:$D$60,D47,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H47">
@@ -4497,7 +4522,7 @@
         <v/>
       </c>
       <c r="G48" s="30">
-        <f>IF(C48="","",(COUNTIFS($D$2:$D$59,D48,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C48)+(COUNTIFS($D$2:$D$59,D48,$C$2:$C$59,C48)+1)/2)/COUNTIFS($D$2:$D$59,D48,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C48="","",(COUNTIFS($D$2:$D$60,D48,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C48)+(COUNTIFS($D$2:$D$60,D48,$C$2:$C$60,C48)+1)/2)/COUNTIFS($D$2:$D$60,D48,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H48">
@@ -4508,7 +4533,10 @@
         <f>IFERROR(B52/B48-1,"")</f>
         <v/>
       </c>
-      <c r="J48" s="30" t="n"/>
+      <c r="J48" s="30">
+        <f>IFERROR((B60/B48)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K48" s="30" t="n"/>
       <c r="L48" s="30" t="n"/>
     </row>
@@ -4536,7 +4564,7 @@
         <v/>
       </c>
       <c r="G49" s="30">
-        <f>IF(C49="","",(COUNTIFS($D$2:$D$59,D49,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C49)+(COUNTIFS($D$2:$D$59,D49,$C$2:$C$59,C49)+1)/2)/COUNTIFS($D$2:$D$59,D49,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C49="","",(COUNTIFS($D$2:$D$60,D49,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C49)+(COUNTIFS($D$2:$D$60,D49,$C$2:$C$60,C49)+1)/2)/COUNTIFS($D$2:$D$60,D49,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H49">
@@ -4575,7 +4603,7 @@
         <v/>
       </c>
       <c r="G50" s="30">
-        <f>IF(C50="","",(COUNTIFS($D$2:$D$59,D50,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C50)+(COUNTIFS($D$2:$D$59,D50,$C$2:$C$59,C50)+1)/2)/COUNTIFS($D$2:$D$59,D50,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C50="","",(COUNTIFS($D$2:$D$60,D50,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C50)+(COUNTIFS($D$2:$D$60,D50,$C$2:$C$60,C50)+1)/2)/COUNTIFS($D$2:$D$60,D50,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H50">
@@ -4614,7 +4642,7 @@
         <v/>
       </c>
       <c r="G51" s="30">
-        <f>IF(C51="","",(COUNTIFS($D$2:$D$59,D51,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C51)+(COUNTIFS($D$2:$D$59,D51,$C$2:$C$59,C51)+1)/2)/COUNTIFS($D$2:$D$59,D51,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C51="","",(COUNTIFS($D$2:$D$60,D51,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C51)+(COUNTIFS($D$2:$D$60,D51,$C$2:$C$60,C51)+1)/2)/COUNTIFS($D$2:$D$60,D51,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H51">
@@ -4653,7 +4681,7 @@
         <v/>
       </c>
       <c r="G52" s="30">
-        <f>IF(C52="","",(COUNTIFS($D$2:$D$59,D52,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C52)+(COUNTIFS($D$2:$D$59,D52,$C$2:$C$59,C52)+1)/2)/COUNTIFS($D$2:$D$59,D52,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C52="","",(COUNTIFS($D$2:$D$60,D52,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C52)+(COUNTIFS($D$2:$D$60,D52,$C$2:$C$60,C52)+1)/2)/COUNTIFS($D$2:$D$60,D52,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H52">
@@ -4692,7 +4720,7 @@
         <v/>
       </c>
       <c r="G53" s="30">
-        <f>IF(C53="","",(COUNTIFS($D$2:$D$59,D53,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C53)+(COUNTIFS($D$2:$D$59,D53,$C$2:$C$59,C53)+1)/2)/COUNTIFS($D$2:$D$59,D53,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C53="","",(COUNTIFS($D$2:$D$60,D53,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C53)+(COUNTIFS($D$2:$D$60,D53,$C$2:$C$60,C53)+1)/2)/COUNTIFS($D$2:$D$60,D53,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H53">
@@ -4731,7 +4759,7 @@
         <v/>
       </c>
       <c r="G54" s="30">
-        <f>IF(C54="","",(COUNTIFS($D$2:$D$59,D54,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C54)+(COUNTIFS($D$2:$D$59,D54,$C$2:$C$59,C54)+1)/2)/COUNTIFS($D$2:$D$59,D54,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C54="","",(COUNTIFS($D$2:$D$60,D54,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C54)+(COUNTIFS($D$2:$D$60,D54,$C$2:$C$60,C54)+1)/2)/COUNTIFS($D$2:$D$60,D54,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H54">
@@ -4770,7 +4798,7 @@
         <v/>
       </c>
       <c r="G55" s="30">
-        <f>IF(C55="","",(COUNTIFS($D$2:$D$59,D55,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C55)+(COUNTIFS($D$2:$D$59,D55,$C$2:$C$59,C55)+1)/2)/COUNTIFS($D$2:$D$59,D55,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C55="","",(COUNTIFS($D$2:$D$60,D55,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C55)+(COUNTIFS($D$2:$D$60,D55,$C$2:$C$60,C55)+1)/2)/COUNTIFS($D$2:$D$60,D55,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H55">
@@ -4809,14 +4837,17 @@
         <v/>
       </c>
       <c r="G56" s="30">
-        <f>IF(C56="","",(COUNTIFS($D$2:$D$59,D56,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C56)+(COUNTIFS($D$2:$D$59,D56,$C$2:$C$59,C56)+1)/2)/COUNTIFS($D$2:$D$59,D56,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C56="","",(COUNTIFS($D$2:$D$60,D56,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C56)+(COUNTIFS($D$2:$D$60,D56,$C$2:$C$60,C56)+1)/2)/COUNTIFS($D$2:$D$60,D56,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H56">
         <f>IF(G56="","",IF(G56&lt;=20%,"Q1 Cheapest",IF(G56&lt;=40%,"Q2",IF(G56&lt;=60%,"Q3",IF(G56&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I56" s="30" t="n"/>
+      <c r="I56" s="30">
+        <f>IFERROR(B60/B56-1,"")</f>
+        <v/>
+      </c>
       <c r="J56" s="30" t="n"/>
       <c r="K56" s="30" t="n"/>
       <c r="L56" s="30" t="n"/>
@@ -4845,7 +4876,7 @@
         <v/>
       </c>
       <c r="G57" s="30">
-        <f>IF(C57="","",(COUNTIFS($D$2:$D$59,D57,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C57)+(COUNTIFS($D$2:$D$59,D57,$C$2:$C$59,C57)+1)/2)/COUNTIFS($D$2:$D$59,D57,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C57="","",(COUNTIFS($D$2:$D$60,D57,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C57)+(COUNTIFS($D$2:$D$60,D57,$C$2:$C$60,C57)+1)/2)/COUNTIFS($D$2:$D$60,D57,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H57">
@@ -4881,7 +4912,7 @@
         <v/>
       </c>
       <c r="G58" s="30">
-        <f>IF(C58="","",(COUNTIFS($D$2:$D$59,D58,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C58)+(COUNTIFS($D$2:$D$59,D58,$C$2:$C$59,C58)+1)/2)/COUNTIFS($D$2:$D$59,D58,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C58="","",(COUNTIFS($D$2:$D$60,D58,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C58)+(COUNTIFS($D$2:$D$60,D58,$C$2:$C$60,C58)+1)/2)/COUNTIFS($D$2:$D$60,D58,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H58">
@@ -4917,7 +4948,7 @@
         <v/>
       </c>
       <c r="G59" s="30">
-        <f>IF(C59="","",(COUNTIFS($D$2:$D$59,D59,$C$2:$C$59,"&gt;0",$C$2:$C$59,"&lt;"&amp;C59)+(COUNTIFS($D$2:$D$59,D59,$C$2:$C$59,C59)+1)/2)/COUNTIFS($D$2:$D$59,D59,$C$2:$C$59,"&gt;0"))</f>
+        <f>IF(C59="","",(COUNTIFS($D$2:$D$60,D59,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C59)+(COUNTIFS($D$2:$D$60,D59,$C$2:$C$60,C59)+1)/2)/COUNTIFS($D$2:$D$60,D59,$C$2:$C$60,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H59">
@@ -4928,6 +4959,42 @@
       <c r="J59" s="30" t="n"/>
       <c r="K59" s="30" t="n"/>
       <c r="L59" s="30" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B60" s="24" t="n">
+        <v>17028.7</v>
+      </c>
+      <c r="C60" s="25" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E60" s="33">
+        <f>IFERROR(B60/C60,"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="30">
+        <f>IF(AND(D60=D56,E56&lt;&gt;""),E60/E56-1,"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="30">
+        <f>IF(C60="","",(COUNTIFS($D$2:$D$60,D60,$C$2:$C$60,"&gt;0",$C$2:$C$60,"&lt;"&amp;C60)+(COUNTIFS($D$2:$D$60,D60,$C$2:$C$60,C60)+1)/2)/COUNTIFS($D$2:$D$60,D60,$C$2:$C$60,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H60">
+        <f>IF(G60="","",IF(G60&lt;=20%,"Q1 Cheapest",IF(G60&lt;=40%,"Q2",IF(G60&lt;=60%,"Q3",IF(G60&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I60" s="30" t="n"/>
+      <c r="J60" s="30" t="n"/>
+      <c r="K60" s="30" t="n"/>
+      <c r="L60" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4942,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4950,7 +5017,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -5264,6 +5331,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>17028.7</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.44776119403</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.168212302102</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5304,7 +5404,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17028.7</v>
+        <v>16840.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.14</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4477611940298508</v>
+        <v>0.4402985074626866</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>564.9867285998673</v>
+        <v>565.1124161073825</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1682123021020248</v>
+        <v>0.1685886925078908</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.033178500331785</v>
+        <v>0.03355704697986577</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>55.22388059701493</v>
+        <v>55.97014925373134</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.64246042040496</v>
+        <v>83.71773850157815</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>63.74945454403193</v>
+        <v>64.29442602808538</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59541878016918</v>
+        <v>24.59882565104285</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13896.08519515153</v>
+        <v>13901.10179706508</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1839608898417657</v>
+        <v>-0.1745360519784278</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00778326647087</v>
+        <v>38.00863498418929</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21473.89312905616</v>
+        <v>21479.15154885879</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2610412497170163</v>
+        <v>0.2754575498050096</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5364,6 +5364,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>16840.35</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.168588692508</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5404,7 +5437,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16840.35</v>
+        <v>16911.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.8</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.1124161073825</v>
+        <v>565.0267290344136</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1685886925078908</v>
+        <v>0.1684302893331022</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03355704697986577</v>
+        <v>0.03341129301703976</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.71773850157815</v>
+        <v>83.68605786662044</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.29442602808538</v>
+        <v>64.28492183759806</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59882565104285</v>
+        <v>24.59739187602077</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13901.10179706508</v>
+        <v>13898.18387448567</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1745360519784278</v>
+        <v>-0.1781693325753169</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00863498418929</v>
+        <v>38.00827654043376</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21479.15154885879</v>
+        <v>21475.69216987672</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2754575498050096</v>
+        <v>0.2699056645651103</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5397,6 +5397,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>16911.25</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.168430289333</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5437,7 +5470,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16911.25</v>
+        <v>17119.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.93</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4402985074626866</v>
+        <v>0.4552238805970149</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.0267290344136</v>
+        <v>565.0066006600661</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1684302893331022</v>
+        <v>0.1684066583178037</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03341129301703976</v>
+        <v>0.033003300330033</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>55.97014925373134</v>
+        <v>54.47761194029851</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.68605786662044</v>
+        <v>83.68133166356073</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.28492183759806</v>
+        <v>63.23872785727717</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59739187602077</v>
+        <v>24.59717798157372</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13898.18387448567</v>
+        <v>13897.56791719959</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1781693325753169</v>
+        <v>-0.1882119478028476</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00827654043376</v>
+        <v>38.008223066822</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21475.69216987672</v>
+        <v>21474.89691211461</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2699056645651103</v>
+        <v>0.2543968008852144</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5430,6 +5430,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>17119.7</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.455223880597</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.168406658318</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5470,7 +5503,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>17119.7</v>
+        <v>16990.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.3</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4552238805970149</v>
+        <v>0.4402985074626866</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.0066006600661</v>
+        <v>565.0432324575988</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1684066583178037</v>
+        <v>0.1685700455159884</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.033003300330033</v>
+        <v>0.03325573661456601</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>54.47761194029851</v>
+        <v>55.97014925373134</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.68133166356073</v>
+        <v>83.71400910319768</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>63.23872785727717</v>
+        <v>64.29330720857124</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59717798157372</v>
+        <v>24.59865686912757</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13897.56791719959</v>
+        <v>13899.30459144716</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1882119478028476</v>
+        <v>-0.1819535460882085</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.008223066822</v>
+        <v>38.00859278871046</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21474.89691211461</v>
+        <v>21476.49813049754</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2543968008852144</v>
+        <v>0.264003750871648</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5463,6 +5463,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>16990.85</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.168570045516</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5503,7 +5536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16990.85</v>
+        <v>16530.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.07</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.0432324575988</v>
+        <v>564.9658236500342</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1685700455159884</v>
+        <v>0.168425426428594</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03325573661456601</v>
+        <v>0.03417634996582364</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.71400910319768</v>
+        <v>83.68508528571881</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.29330720857124</v>
+        <v>64.28463006332757</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59865686912757</v>
+        <v>24.59734785978796</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13899.30459144716</v>
+        <v>13896.66089321151</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1819535460882085</v>
+        <v>-0.1593524313127835</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00859278871046</v>
+        <v>38.00826553637556</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21476.49813049754</v>
+        <v>21473.37104426763</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.264003750871648</v>
+        <v>0.2989837845651251</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5496,6 +5496,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>16530.9</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.168425426429</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5536,7 +5569,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16530.9</v>
+        <v>16786.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.26</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>564.9658236500342</v>
+        <v>565.0185122854258</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.168425426428594</v>
+        <v>0.1685156251387814</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03417634996582364</v>
+        <v>0.03365870077415012</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.68508528571881</v>
+        <v>83.70312502775627</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.28463006332757</v>
+        <v>64.29004198593881</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59734785978796</v>
+        <v>24.59816428697046</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13896.66089321151</v>
+        <v>13898.41819037654</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1593524313127835</v>
+        <v>-0.1720577486714757</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00826553637556</v>
+        <v>38.00846964317118</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21473.37104426763</v>
+        <v>21475.48897203035</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2989837845651251</v>
+        <v>0.2793157066028671</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5529,6 +5529,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>16786.7</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.168515625139</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5569,7 +5602,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16786.7</v>
+        <v>16827.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.71</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.0185122854258</v>
+        <v>565.0654801880457</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1685156251387814</v>
+        <v>0.1685509850504658</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03365870077415012</v>
+        <v>0.0335795836131632</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.70312502775627</v>
+        <v>83.71019701009317</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.29004198593881</v>
+        <v>64.29216358063988</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59816428697046</v>
+        <v>24.59848434468536</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13898.41819037654</v>
+        <v>13899.75436812776</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1720577486714757</v>
+        <v>-0.1739931381905522</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00846964317118</v>
+        <v>38.00854965759991</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21475.48897203035</v>
+        <v>21477.31936352287</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2793157066028671</v>
+        <v>0.2763112712424416</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5562,6 +5562,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>16827.65</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>29.78</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.16855098505</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5602,7 +5635,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16827.65</v>
+        <v>16974</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.78</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.0654801880457</v>
+        <v>565.0466045272969</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1685509850504658</v>
+        <v>0.1685073802484767</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0335795836131632</v>
+        <v>0.03328894806924101</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.71019701009317</v>
+        <v>83.70147604969533</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.29216358063988</v>
+        <v>64.28954729252052</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59848434468536</v>
+        <v>24.59808965893478</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13899.75436812776</v>
+        <v>13899.06703963911</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1739931381905522</v>
+        <v>-0.1811554707411857</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00854965759991</v>
+        <v>38.00845098616226</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21477.31936352287</v>
+        <v>21476.54617307318</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2763112712424416</v>
+        <v>0.2652613510706479</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5595,6 +5595,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>16974</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.168507380248</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5635,7 +5668,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16974</v>
+        <v>16997.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.04</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.0466045272969</v>
+        <v>565.0714760638298</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1685073802484767</v>
+        <v>0.1684816147208601</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03328894806924101</v>
+        <v>0.03324468085106383</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.70147604969533</v>
+        <v>83.69632294417202</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.28954729252052</v>
+        <v>64.28800136086353</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59808965893478</v>
+        <v>24.59785644410195</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13899.06703963911</v>
+        <v>13899.54704887488</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1811554707411857</v>
+        <v>-0.1822521128955467</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00845098616226</v>
+        <v>38.00839268245406</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21476.54617307318</v>
+        <v>21477.45855588798</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2652613510706479</v>
+        <v>0.2635768843900952</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5628,6 +5628,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>16997.35</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.168481614721</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5668,7 +5701,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16997.35</v>
+        <v>16956.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.08</v>
+        <v>29.91</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>565.0714760638298</v>
+        <v>566.9107321965897</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1684816147208601</v>
+        <v>0.1703178415788671</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03324468085106383</v>
+        <v>0.03343363423604146</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.69632294417202</v>
+        <v>84.06356831577342</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.28800136086353</v>
+        <v>64.39817497234395</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59785644410195</v>
+        <v>24.61447692034814</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13899.54704887488</v>
+        <v>13954.21113355062</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1822521128955467</v>
+        <v>-0.1770485817335962</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00839268245406</v>
+        <v>38.04885397311301</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21477.45855588798</v>
+        <v>21570.30366513862</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2635768843900952</v>
+        <v>0.2721114668376132</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5661,6 +5661,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>16956.3</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.170317841579</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5701,7 +5734,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16956.3</v>
+        <v>16946.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.91</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>566.9107321965897</v>
+        <v>566.3870320855615</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1703178415788671</v>
+        <v>0.1677978659476496</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03343363423604146</v>
+        <v>0.03342245989304812</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.06356831577342</v>
+        <v>83.55957318952991</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.39817497234395</v>
+        <v>64.24697643447089</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.61447692034814</v>
+        <v>24.59166754092044</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13954.21113355062</v>
+        <v>13928.40159253677</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1770485817335962</v>
+        <v>-0.1780859779104131</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.04885397311301</v>
+        <v>38.00684545665868</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21570.30366513862</v>
+        <v>21526.58439713152</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2721114668376132</v>
+        <v>0.2702822679364532</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5694,6 +5694,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>16946.3</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.167797865948</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5734,7 +5767,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16946.3</v>
+        <v>16767.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.92</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>566.3870320855615</v>
+        <v>570.7232811436351</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1677978659476496</v>
+        <v>0.1767984505680831</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03342245989304812</v>
+        <v>0.03403675970047652</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.55957318952991</v>
+        <v>85.35969011361662</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.24697643447089</v>
+        <v>64.78701151169692</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.59166754092044</v>
+        <v>24.70783922428348</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>13928.40159253677</v>
+        <v>14101.33907205247</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1780859779104131</v>
+        <v>-0.1590252136050553</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.00684545665868</v>
+        <v>38.27249053131801</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21526.58439713152</v>
+        <v>21843.00137357252</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.2702822679364532</v>
+        <v>0.302671563353234</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5727,6 +5727,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>16767.85</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.176798450568</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5767,7 +5800,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16767.85</v>
+        <v>16500.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>29.38</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>570.7232811436351</v>
+        <v>570.7436873054306</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1767984505680831</v>
+        <v>0.1995826105460499</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03403675970047652</v>
+        <v>0.03459010722933241</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>85.35969011361662</v>
+        <v>89.91652210920998</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>64.78701151169692</v>
+        <v>66.15406111037493</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>24.70783922428348</v>
+        <v>26.19018531878571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>14101.33907205247</v>
+        <v>14947.88294005631</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.1590252136050553</v>
+        <v>-0.09407868146711496</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.27249053131801</v>
+        <v>38.86454324056002</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>21843.00137357252</v>
+        <v>22181.69271455857</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.302671563353234</v>
+        <v>0.344328718109997</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5760,6 +5760,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>16500.2</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.199582610546</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5800,7 +5833,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16500.2</v>
+        <v>16410.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.91</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>570.7436873054306</v>
+        <v>572.6029309141661</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1995826105460499</v>
+        <v>0.2034903476816767</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03459010722933241</v>
+        <v>0.03489183531053733</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>89.91652210920998</v>
+        <v>90.69806953633535</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>66.15406111037493</v>
+        <v>66.38852533851254</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.19018531878571</v>
+        <v>26.77158961478753</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>14947.88294005631</v>
+        <v>15329.49067865859</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.09407868146711496</v>
+        <v>-0.06589010415954188</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.86454324056002</v>
+        <v>38.93970577312299</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22181.69271455857</v>
+        <v>22296.9896546255</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.344328718109997</v>
+        <v>0.3586778008765874</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5793,6 +5793,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>16410.8</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.440298507463</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.203490347682</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5833,7 +5866,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16410.8</v>
+        <v>16066.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.66</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.4402985074626866</v>
+        <v>0.4104477611940299</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>572.6029309141661</v>
+        <v>573.3904354032834</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2034903476816767</v>
+        <v>0.2052155648604046</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03489183531053733</v>
+        <v>0.03568879371877231</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>55.97014925373134</v>
+        <v>58.95522388059702</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>90.69806953633535</v>
+        <v>91.04311297208092</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>66.38852533851254</v>
+        <v>68.58159060804218</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.77158961478753</v>
+        <v>27.0282723558306</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>15329.49067865859</v>
+        <v>15497.75285430824</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.06589010415954188</v>
+        <v>-0.03539356331796573</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.93970577312299</v>
+        <v>38.96985636543246</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22296.9896546255</v>
+        <v>22344.94290897873</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3586778008765874</v>
+        <v>0.390787165076105</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5826,6 +5826,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>16066.4</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.410447761194</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.20521556486</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5866,7 +5899,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16066.4</v>
+        <v>16266.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.02</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>573.3904354032834</v>
+        <v>573.3820937610152</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2052155648604046</v>
+        <v>0.2059085189754157</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03568879371877231</v>
+        <v>0.0352485019386676</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>91.04311297208092</v>
+        <v>91.18170379508315</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.58159060804218</v>
+        <v>68.62316785494285</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.0282723558306</v>
+        <v>27.13137204893084</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>15497.75285430824</v>
+        <v>15556.64291202505</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.03539356331796573</v>
+        <v>-0.04365977973454915</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.96985636543246</v>
+        <v>38.98004873052983</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22344.94290897873</v>
+        <v>22350.4619560176</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.390787165076105</v>
+        <v>0.3739883232474386</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5859,6 +5859,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>16266.85</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.410447761194</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.205908518975</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5899,7 +5932,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16266.85</v>
+        <v>16412.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.37</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>573.3820937610152</v>
+        <v>589.7484728710026</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2059085189754157</v>
+        <v>0.2357581114539389</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0352485019386676</v>
+        <v>0.03593244699964068</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>91.18170379508315</v>
+        <v>97.15162229078777</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>68.62316785494285</v>
+        <v>70.41414340365424</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>27.13137204893084</v>
+        <v>28.15642060747381</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>15556.64291202505</v>
+        <v>16605.2060547713</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>-0.04365977973454915</v>
+        <v>0.01172909117764309</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>38.98004873052983</v>
+        <v>40.18483818443676</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>22350.4619560176</v>
+        <v>23698.94695183993</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3739883232474386</v>
+        <v>0.4439395682514109</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5892,6 +5892,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>16412.7</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.410447761194</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.235758111454</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5932,7 +5965,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16412.7</v>
+        <v>16500.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.83</v>
+        <v>28.04</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>589.7484728710026</v>
+        <v>588.4682596291013</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2357581114539389</v>
+        <v>0.2317646435588248</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03593244699964068</v>
+        <v>0.03566333808844508</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.15162229078777</v>
+        <v>96.35292871176495</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.41414340365424</v>
+        <v>70.17453532994739</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.15642060747381</v>
+        <v>28.15943363702407</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16605.2060547713</v>
+        <v>16570.93290452073</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01172909117764309</v>
+        <v>0.004259402176321814</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>40.18483818443676</v>
+        <v>39.90018379287302</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>23698.94695183993</v>
+        <v>23479.99171547326</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4439395682514109</v>
+        <v>0.4229737443963275</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5925,6 +5925,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>16500.65</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.410447761194</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.231764643559</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5965,7 +5998,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16500.65</v>
+        <v>16656.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.04</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>588.4682596291013</v>
+        <v>588.1497175141243</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2317646435588248</v>
+        <v>0.2350334407908812</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03566333808844508</v>
+        <v>0.03531073446327684</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>96.35292871176495</v>
+        <v>97.00668815817623</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.17453532994739</v>
+        <v>70.37066316387077</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.15943363702407</v>
+        <v>28.40341658358656</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16570.93290452073</v>
+        <v>16705.46144007242</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.004259402176321814</v>
+        <v>0.002945500832858494</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>39.90018379287302</v>
+        <v>40.133183659574</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>23479.99171547326</v>
+        <v>23604.32063232092</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4229737443963275</v>
+        <v>0.4171321913691384</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5958,6 +5958,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>16656.4</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.410447761194</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.235033440791</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5998,7 +6031,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-midcap-50.xlsx
+++ b/docs/downloads/indices/nifty-midcap-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>16656.4</v>
+        <v>16513.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.32</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>588.1497175141243</v>
+        <v>594.6453006841915</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.2350334407908812</v>
+        <v>0.2487647212245248</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03531073446327684</v>
+        <v>0.03601008282319049</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>97.00668815817623</v>
+        <v>99.75294424490495</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.37066316387077</v>
+        <v>71.19453998988939</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>28.40341658358656</v>
+        <v>28.51215832800702</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>16705.46144007242</v>
+        <v>16954.62096211301</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.002945500832858494</v>
+        <v>0.02672518285945324</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>40.133183659574</v>
+        <v>40.94643879036686</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>23604.32063232092</v>
+        <v>24348.60740644454</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4171321913691384</v>
+        <v>0.4744846521558104</v>
       </c>
     </row>
     <row r="16">
@@ -5009,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5991,6 +5991,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>16513.3</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.410447761194</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.248764721225</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -6031,7 +6064,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
